--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-06-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_20-06-2025.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/25mm-recticel-insulation-boards/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£11.04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£12.68</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£16.26</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£16.54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£22.88</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£23.21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£26.46</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£28.96</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£28.26</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/120mm-recticel-insulation-boards/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£34.66</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£42.27</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£43.26</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£43.05</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£399.4</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£437.65</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£457.84</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
